--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484889_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484889_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2257</v>
+        <v>10.9935</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8286</v>
+        <v>8.8873</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3971</v>
+        <v>2.1061</v>
       </c>
       <c r="G2" t="n">
         <v>9.516500000000001</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9353</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1735</v>
+        <v>-0.1147</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1088</v>
+        <v>0.8178</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9244</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.6105</v>
+        <v>9.749499999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5997</v>
+        <v>6.0297</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0107</v>
+        <v>3.7197</v>
       </c>
       <c r="G3" t="n">
         <v>5.3689</v>
@@ -688,13 +688,13 @@
         <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6755</v>
+        <v>0.8145</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4674</v>
+        <v>-0.0374</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1429</v>
+        <v>0.8519</v>
       </c>
       <c r="V3" t="n">
         <v>1.8678</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.0543</v>
+        <v>8.2029</v>
       </c>
       <c r="E4" t="n">
-        <v>8.0543</v>
+        <v>5.1284</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.0744</v>
       </c>
       <c r="G4" t="n">
-        <v>8.0543</v>
+        <v>6.4333</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2678</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>6.7865</v>
+        <v>5.8189</v>
       </c>
       <c r="J4" t="n">
-        <v>8.0543</v>
+        <v>5.4117</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2678</v>
+        <v>0.6973</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7865</v>
+        <v>4.7144</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.0216</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.0829</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.1045</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.0148</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.9206</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.8683</v>
+        <v>8.0543</v>
       </c>
       <c r="E5" t="n">
-        <v>4.27</v>
+        <v>8.0543</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5983</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4333</v>
+        <v>8.0543</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6143999999999999</v>
+        <v>1.2678</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8189</v>
+        <v>6.7865</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4117</v>
+        <v>8.0543</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6973</v>
+        <v>1.2678</v>
       </c>
       <c r="L5" t="n">
-        <v>4.7144</v>
+        <v>6.7865</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0216</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0829</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1045</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3198</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7642</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4445</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1918</v>
+        <v>6.0398</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2207</v>
+        <v>4.9099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9712</v>
+        <v>1.1299</v>
       </c>
       <c r="G6" t="n">
         <v>4.956</v>
@@ -922,13 +922,13 @@
         <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9905</v>
+        <v>0.8384</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5937</v>
+        <v>0.2829</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3969</v>
+        <v>0.5556</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3208</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.4917</v>
+        <v>5.0537</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7789</v>
+        <v>3.1557</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7128</v>
+        <v>1.898</v>
       </c>
       <c r="G7" t="n">
         <v>3.2288</v>
@@ -1000,13 +1000,13 @@
         <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4326</v>
+        <v>-0.0054</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4761</v>
+        <v>-0.1472</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0435</v>
+        <v>0.1417</v>
       </c>
       <c r="V7" t="n">
         <v>1.2642</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2557</v>
+        <v>4.2112</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6996</v>
+        <v>-0.4915</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5561</v>
+        <v>4.7027</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3333</v>
+        <v>2.5245</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2119</v>
+        <v>1.1301</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1214</v>
+        <v>1.3944</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8411</v>
+        <v>1.9525</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6766</v>
+        <v>1.2944</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1645</v>
+        <v>0.6581</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4922</v>
+        <v>0.572</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5353</v>
+        <v>-0.1643</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0431</v>
+        <v>0.7363</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2644</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>3.2079</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4127</v>
+        <v>0.4224</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1793</v>
+        <v>-0.1796</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2334</v>
+        <v>0.602</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1886</v>
+        <v>0.3208</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8678</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.8323</v>
+        <v>4.0751</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1349</v>
+        <v>3.4661</v>
       </c>
       <c r="F9" t="n">
-        <v>4.9673</v>
+        <v>0.609</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5245</v>
+        <v>4.3333</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1301</v>
+        <v>4.2119</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3944</v>
+        <v>0.1214</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9525</v>
+        <v>3.8411</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2944</v>
+        <v>3.6766</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6581</v>
+        <v>0.1645</v>
       </c>
       <c r="M9" t="n">
-        <v>0.572</v>
+        <v>0.4922</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1643</v>
+        <v>0.5353</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7363</v>
+        <v>-0.0431</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2644</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2079</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0436</v>
+        <v>0.2321</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.823</v>
+        <v>-0.0543</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8666</v>
+        <v>0.2863</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3208</v>
+        <v>-2.1886</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3208</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7837</v>
+        <v>3.5221</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9522</v>
+        <v>1.494</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8316</v>
+        <v>2.0281</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8086</v>
+        <v>5.0844</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0925</v>
+        <v>1.7483</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2839</v>
+        <v>3.3361</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1821</v>
+        <v>4.2785</v>
       </c>
       <c r="K10" t="n">
-        <v>1.094</v>
+        <v>0.8561</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9119</v>
+        <v>3.4223</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0015</v>
+        <v>0.8922</v>
       </c>
       <c r="O10" t="n">
-        <v>0.628</v>
+        <v>-0.0863</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9435</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0316</v>
+        <v>0.4193</v>
       </c>
       <c r="T10" t="n">
-        <v>0.77</v>
+        <v>-0.2368</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2616</v>
+        <v>0.6561</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.7948</v>
+        <v>2.7939</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0841</v>
+        <v>0.465</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7107</v>
+        <v>2.3289</v>
       </c>
       <c r="G11" t="n">
-        <v>5.0844</v>
+        <v>0.8086</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7483</v>
+        <v>1.0925</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3361</v>
+        <v>-0.2839</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2785</v>
+        <v>0.1821</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8561</v>
+        <v>1.094</v>
       </c>
       <c r="L11" t="n">
-        <v>3.4223</v>
+        <v>-0.9119</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8922</v>
+        <v>-0.0015</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0863</v>
+        <v>0.628</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.308</v>
+        <v>1.0418</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.2829</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3386</v>
+        <v>0.759</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.29</v>
+        <v>1.9507</v>
       </c>
       <c r="E12" t="n">
-        <v>1.157</v>
+        <v>0.9235</v>
       </c>
       <c r="F12" t="n">
-        <v>1.133</v>
+        <v>1.0272</v>
       </c>
       <c r="G12" t="n">
         <v>1.2407</v>
@@ -1390,13 +1390,13 @@
         <v>0.1887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8606</v>
+        <v>0.5213</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4144</v>
+        <v>0.1809</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4462</v>
+        <v>0.3404</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.768</v>
+        <v>1.696</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8915</v>
+        <v>-0.2279</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6594</v>
+        <v>1.924</v>
       </c>
       <c r="G13" t="n">
         <v>1.0189</v>
@@ -1468,13 +1468,13 @@
         <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4021</v>
+        <v>0.526</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7055</v>
+        <v>-0.0419</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3034</v>
+        <v>0.5679</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6036</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>65.16680000000001</v>
+        <v>66.34269999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>40.6187</v>
+        <v>41.7945</v>
       </c>
       <c r="F14" t="n">
-        <v>24.5482</v>
+        <v>24.548</v>
       </c>
       <c r="G14" t="n">
         <v>52.5682</v>
@@ -1516,7 +1516,7 @@
         <v>22.5858</v>
       </c>
       <c r="I14" t="n">
-        <v>29.9824</v>
+        <v>29.98240000000001</v>
       </c>
       <c r="J14" t="n">
         <v>47.2201</v>
@@ -1546,13 +1546,13 @@
         <v>17.9265</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3525</v>
+        <v>6.5283</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1468</v>
+        <v>0.02899999999999996</v>
       </c>
       <c r="U14" t="n">
-        <v>6.499400000000001</v>
+        <v>6.499300000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3018000000000002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.5008</v>
+        <v>-2.2349</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.952</v>
+        <v>-1.6597</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5488</v>
+        <v>-0.5752</v>
       </c>
       <c r="G15" t="n">
         <v>-1.9272</v>
@@ -1624,13 +1624,13 @@
         <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6302</v>
+        <v>-0.3643</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7642</v>
+        <v>-0.4719</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1341</v>
+        <v>0.1076</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3208</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.3564</v>
+        <v>-4.4635</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6808</v>
+        <v>0.3885</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.0372</v>
+        <v>-4.852</v>
       </c>
       <c r="G16" t="n">
         <v>-6.6998</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4862</v>
+        <v>-0.5933</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4057</v>
+        <v>-0.698</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0805</v>
+        <v>0.1047</v>
       </c>
       <c r="V16" t="n">
         <v>4.3392</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.1413</v>
+        <v>-4.8852</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6707</v>
+        <v>-2.5733</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4706</v>
+        <v>-2.3119</v>
       </c>
       <c r="G17" t="n">
         <v>-4.0765</v>
@@ -1780,13 +1780,13 @@
         <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8007</v>
+        <v>-0.5445</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6343</v>
+        <v>-0.5369</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1663</v>
+        <v>-0.0076</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6415999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.896</v>
+        <v>-5.2055</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4951</v>
+        <v>-1.9105</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4009</v>
+        <v>-3.295</v>
       </c>
       <c r="G18" t="n">
         <v>-4.3517</v>
@@ -1858,13 +1858,13 @@
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1669</v>
+        <v>-0.4765</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1634</v>
+        <v>-0.5788</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0035</v>
+        <v>0.1023</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.9497</v>
+        <v>-6.3562</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5886</v>
+        <v>-1.7834</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.3611</v>
+        <v>-4.5728</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8697</v>
@@ -1936,13 +1936,13 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2122</v>
+        <v>-0.6187</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.749</v>
+        <v>-0.9439</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.3252</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4904</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.1289</v>
+        <v>-7.8114</v>
       </c>
       <c r="E20" t="n">
         <v>-2.0858</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.0431</v>
+        <v>-5.7256</v>
       </c>
       <c r="G20" t="n">
         <v>-7.3092</v>
@@ -2014,13 +2014,13 @@
         <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3292</v>
+        <v>-1.0117</v>
       </c>
       <c r="T20" t="n">
         <v>-0.8789</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4503</v>
+        <v>-0.1328</v>
       </c>
       <c r="V20" t="n">
         <v>0.3208</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. CASTELLANOS MARTINEZ</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.219900000000001</v>
+        <v>-9.957700000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4329</v>
+        <v>-4.1327</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.7869</v>
+        <v>-5.825</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.5146</v>
+        <v>-9.15</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6694</v>
+        <v>-2.7743</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.8452</v>
+        <v>-6.3757</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7232</v>
+        <v>-2.0621</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1432</v>
+        <v>-0.1887</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8664</v>
+        <v>-1.8735</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.7914</v>
+        <v>-7.0879</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.8126</v>
+        <v>-2.5857</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.9787</v>
+        <v>-4.5022</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7548</v>
+        <v>-1.887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1887</v>
+        <v>-3.2079</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9435</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4643</v>
+        <v>-0.1849</v>
       </c>
       <c r="T21" t="n">
-        <v>0.479</v>
+        <v>-0.7305</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0147</v>
+        <v>0.5456</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9244</v>
+        <v>1.2642</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9244</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>C. CASTELLANOS MARTINEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.861599999999999</v>
+        <v>-10.3</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3276</v>
+        <v>-2.4073</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.534</v>
+        <v>-7.8927</v>
       </c>
       <c r="G22" t="n">
-        <v>-9.15</v>
+        <v>-9.5146</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7743</v>
+        <v>-2.6694</v>
       </c>
       <c r="I22" t="n">
-        <v>-6.3757</v>
+        <v>-6.8452</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0621</v>
+        <v>-1.7232</v>
       </c>
       <c r="K22" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.8664</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-7.7914</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-2.8126</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-4.9787</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.1887</v>
       </c>
-      <c r="L22" t="n">
-        <v>-1.8735</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-7.0879</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-2.5857</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-4.5022</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-1.887</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-3.2079</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.3209</v>
+        <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0888</v>
+        <v>-0.6158</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9254</v>
+        <v>-0.4953</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8366</v>
+        <v>-0.1205</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2642</v>
+        <v>-0.9244</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6036</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.1123</v>
+        <v>-13.9523</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.6762</v>
+        <v>-8.383900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4361</v>
+        <v>-5.5683</v>
       </c>
       <c r="G23" t="n">
         <v>-6.6694</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1028</v>
+        <v>-0.9428</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4574</v>
+        <v>-1.165</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3545</v>
+        <v>0.2223</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-65.1669</v>
+        <v>-65.16669999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-24.5481</v>
       </c>
       <c r="F24" t="n">
-        <v>-40.61869999999999</v>
+        <v>-40.6185</v>
       </c>
       <c r="G24" t="n">
         <v>-52.5681</v>
@@ -2326,13 +2326,13 @@
         <v>10.3785</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.3527</v>
+        <v>-5.3525</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.4993</v>
+        <v>-6.499199999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1467</v>
+        <v>1.1468</v>
       </c>
       <c r="V24" t="n">
         <v>0.3017999999999996</v>
